--- a/ABA_mining/outputs/eval/task3/price/llama3.2/one_shot/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/price/llama3.2/one_shot/EVAL_SUMMARY.xlsx
@@ -550,7 +550,7 @@
         <v>0.392</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.331868</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>0.392</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.331868</v>
       </c>
     </row>
     <row r="4">
@@ -668,7 +668,7 @@
         <v>0.392</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.331868</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +793,7 @@
         <v>0.392</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3318681318681319</v>
+        <v>0.331868</v>
       </c>
       <c r="J2" t="n">
         <v>1365</v>
